--- a/Vf/TABLE_4_5/Table_5_PanelD_Multiplicative_MIDAS.xlsx
+++ b/Vf/TABLE_4_5/Table_5_PanelD_Multiplicative_MIDAS.xlsx
@@ -484,13 +484,13 @@
         <v>1.100785055980052</v>
       </c>
       <c r="C4" t="n">
-        <v>1.134229035816607</v>
+        <v>1.134083047194954</v>
       </c>
       <c r="D4" t="n">
-        <v>1.14992279958566</v>
+        <v>1.149930775281364</v>
       </c>
       <c r="E4" t="n">
-        <v>1.159423341113643</v>
+        <v>1.159414095737177</v>
       </c>
     </row>
     <row r="5">
@@ -515,10 +515,10 @@
         <v>0.95</v>
       </c>
       <c r="B6" t="n">
-        <v>1.142275731783936</v>
+        <v>1.138788564248178</v>
       </c>
       <c r="C6" t="n">
-        <v>1.194081240882344</v>
+        <v>1.193406014717582</v>
       </c>
       <c r="D6" t="n">
         <v>1.20260454647851</v>
